--- a/初中/物理/输出/上海初中物理-考点公式清单.xlsx
+++ b/初中/物理/输出/上海初中物理-考点公式清单.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公式表'!$A$1:$E$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'关系边'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'关卡地图'!$A$1:$F$3</definedName>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,17 +538,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A-1.1</t>
+          <t>A-0.1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>声波的产生和传播</t>
+          <t>长度与时间的测量</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>声 · 单元一：声现象</t>
+          <t>序章 · 单元零：测量的历史与单位</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -558,37 +558,33 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>宇航员在月球上面对面说话，能听见吗？为什么？</t>
+          <t>刻度尺读数时，要估读到分度值的下一位吗？</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>01-声-单元一-声现象.md</t>
+          <t>00-序章-单元零-测量与单位.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>A-1.2</t>
+          <t>A-1.1</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>声音的特征</t>
+          <t>声波的产生和传播</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -616,7 +612,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>用力敲鼓和轻轻敲鼓，改变的是音调还是响度？</t>
+          <t>宇航员在月球上面对面说话，能听见吗？为什么？</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -628,17 +624,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>A-1.2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>光的反射</t>
+          <t>声音的特征</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>光 · 单元二：光现象</t>
+          <t>声 · 单元一：声现象</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -651,30 +647,34 @@
           <t>高</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>入射角是 30°，反射角是多少？</t>
+          <t>用力敲鼓和轻轻敲鼓，改变的是音调还是响度？</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>02-光-单元二-光现象.md</t>
+          <t>01-声-单元一-声现象.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>A-2.2</t>
+          <t>A-2.1</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>平面镜成像</t>
+          <t>光的反射</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -692,17 +692,13 @@
           <t>高</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>人往平面镜走近 1 m，像离人变近多少？</t>
+          <t>入射角是 30°，反射角是多少？</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -714,12 +710,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A-2.3</t>
+          <t>A-2.2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>光的折射</t>
+          <t>平面镜成像</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -747,7 +743,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>筷子插进水里，为什么看起来"折断"了？</t>
+          <t>人往平面镜走近 1 m，像离人变近多少？</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -759,12 +755,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>A-2.4</t>
+          <t>A-2.3</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>透镜成像</t>
+          <t>光的折射</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -792,7 +788,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>放大镜成的是实像还是虚像？</t>
+          <t>筷子插进水里，为什么看起来"折断"了？</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -804,12 +800,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A-2.5</t>
+          <t>A-2.4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>光的色散</t>
+          <t>透镜成像</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -819,21 +815,25 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ</t>
+          <t>Ⅱ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>白光是单色光还是复色光？</t>
+          <t>放大镜成的是实像还是虚像？</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -845,17 +845,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>A-3.1</t>
+          <t>A-2.5</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>机械运动</t>
+          <t>光的色散</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>运动和力 · 单元三：力与运动</t>
+          <t>光 · 单元二：光现象</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -874,24 +874,24 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>坐在行驶的车里，你是运动的还是静止的？</t>
+          <t>白光是单色光还是复色光？</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>03-力与运动-单元三-运动和力.md</t>
+          <t>02-光-单元二-光现象.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>A-3.2</t>
+          <t>A-3.1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>直线运动</t>
+          <t>机械运动</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -901,25 +901,21 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ</t>
+          <t>Ⅰ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>100 m 跑 12.5 s，速度是多少 km/h？</t>
+          <t>坐在行驶的车里，你是运动的还是静止的？</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -931,12 +927,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>A-3.3</t>
+          <t>A-3.2</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>直线运动</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -951,16 +947,20 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>力能脱离物体单独存在吗？</t>
+          <t>100 m 跑 12.5 s，速度是多少 km/h？</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -972,12 +972,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>A-3.4</t>
+          <t>A-3.3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>力</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -992,20 +992,16 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>把物体带到月球，它的质量和重力各怎么变？</t>
+          <t>力能脱离物体单独存在吗？</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1017,12 +1013,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>A-3.5</t>
+          <t>A-3.4</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>力的合成</t>
+          <t>重力</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1037,16 +1033,20 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>3 N 和 4 N 的两个力，合力一定是 7 N 吗？</t>
+          <t>把物体带到月球，它的质量和重力各怎么变？</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1058,12 +1058,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>A-3.6</t>
+          <t>A-3.5</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>二力平衡</t>
+          <t>力的合成</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1078,20 +1078,16 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>静止在桌上的书，受几个力？它们什么关系？</t>
+          <t>3 N 和 4 N 的两个力，合力一定是 7 N 吗？</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1103,12 +1099,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>A-3.7</t>
+          <t>A-3.6</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>惯性 牛顿第一定律</t>
+          <t>二力平衡</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1136,7 +1132,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>汽车急刹车时，人为什么向前倾？</t>
+          <t>静止在桌上的书，受几个力？它们什么关系？</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1148,17 +1144,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>A-4.1</t>
+          <t>A-3.7</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>杠杆</t>
+          <t>惯性 牛顿第一定律</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>机械和功 · 单元四：简单机械与功</t>
+          <t>运动和力 · 单元三：力与运动</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1181,24 +1177,24 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>用撬棒撬石头，手离支点越远越省力还是越费力？</t>
+          <t>汽车急刹车时，人为什么向前倾？</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>04-机械和功-单元四-简单机械与功.md</t>
+          <t>03-力与运动-单元三-运动和力.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A-4.2</t>
+          <t>A-4.1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>滑轮</t>
+          <t>杠杆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1226,7 +1222,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>定滑轮能省力吗？</t>
+          <t>用撬棒撬石头，手离支点越远越省力还是越费力？</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1238,12 +1234,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>A-4.3</t>
+          <t>A-4.2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>功与功率</t>
+          <t>滑轮</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1271,7 +1267,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>推着箱子原地不动，人对箱子做功了吗？</t>
+          <t>定滑轮能省力吗？</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1283,12 +1279,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A-4.4</t>
+          <t>A-4.3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>机械能</t>
+          <t>功与功率</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1303,16 +1299,20 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>滚摆上升时，动能和势能怎么变？</t>
+          <t>推着箱子原地不动，人对箱子做功了吗？</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A-4.5</t>
+          <t>A-4.4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>机械效率与功的原理</t>
+          <t>机械能</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1344,20 +1344,16 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>使用任何机械都不能省功，那为什么还要用机械？</t>
+          <t>滚摆上升时，动能和势能怎么变？</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1369,53 +1365,57 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A-5.1</t>
+          <t>A-4.5</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>温度与温标</t>
+          <t>机械效率与功的原理</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>热与能 · 单元五：热现象</t>
+          <t>机械和功 · 单元四：简单机械与功</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ</t>
+          <t>Ⅱ</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>0 ℃ 的冰和 0 ℃ 的水，温度相同吗？</t>
+          <t>使用任何机械都不能省功，那为什么还要用机械？</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>05-热与能-单元五-热现象.md</t>
+          <t>04-机械和功-单元四-简单机械与功.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A-5.2</t>
+          <t>A-5.1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>热量与比热容</t>
+          <t>温度与温标</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1425,25 +1425,21 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ</t>
+          <t>Ⅰ</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>同样加热，水和沙子谁的温升快？</t>
+          <t>0 ℃ 的冰和 0 ℃ 的水，温度相同吗？</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1455,12 +1451,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>A-5.3</t>
+          <t>A-5.2</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>内能</t>
+          <t>热量与比热容</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1488,7 +1484,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>0 ℃ 的冰有内能吗？</t>
+          <t>同样加热，水和沙子谁的温升快？</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1500,12 +1496,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>A-5.4</t>
+          <t>A-5.3</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>物态变化</t>
+          <t>内能</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>夏天从冰箱拿出的饮料瓶外壁"出汗"，是水渗出来了吗？</t>
+          <t>0 ℃ 的冰有内能吗？</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1545,12 +1541,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>A-5.5</t>
+          <t>A-5.4</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>热机</t>
+          <t>物态变化</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1565,16 +1561,20 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>汽油机一个工作循环，活塞往复几次？</t>
+          <t>夏天从冰箱拿出的饮料瓶外壁"出汗"，是水渗出来了吗？</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -1586,17 +1586,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A-6.1</t>
+          <t>A-5.5</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>密度</t>
+          <t>热机</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>压力与压强 · 单元六：压强与浮力</t>
+          <t>热与能 · 单元五：热现象</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1606,37 +1606,33 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>铁块和木块，谁重？</t>
+          <t>汽油机一个工作循环，活塞往复几次？</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>06-压强与浮力-单元六-压力与压强.md</t>
+          <t>05-热与能-单元五-热现象.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>A-6.2</t>
+          <t>A-6.1</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>压强</t>
+          <t>密度</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>为什么刀要磨得锋利？</t>
+          <t>铁块和木块，谁重？</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -1676,12 +1672,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>A-6.3</t>
+          <t>A-6.2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>液体内部的压强</t>
+          <t>压强</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1709,7 +1705,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>液体压强与容器形状有关吗？</t>
+          <t>为什么刀要磨得锋利？</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1721,12 +1717,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A-6.4</t>
+          <t>A-6.3</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>阿基米德原理</t>
+          <t>液体内部的压强</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1754,7 +1750,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>物体浸得越深，浮力越大吗？</t>
+          <t>液体压强与容器形状有关吗？</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -1766,12 +1762,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A-6.5</t>
+          <t>A-6.4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>浮沉条件</t>
+          <t>阿基米德原理</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1799,7 +1795,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>物体漂浮时，浮力与重力什么关系？</t>
+          <t>物体浸得越深，浮力越大吗？</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1811,12 +1807,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A-6.6</t>
+          <t>A-6.5</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>大气压强</t>
+          <t>浮沉条件</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1831,16 +1827,20 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>为什么用吸管能把饮料吸上来？</t>
+          <t>物体漂浮时，浮力与重力什么关系？</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A-6.7</t>
+          <t>A-6.6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>流体压强与流速</t>
+          <t>大气压强</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ</t>
+          <t>Ⅱ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>飞机为什么能飞起来？</t>
+          <t>为什么用吸管能把饮料吸上来？</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -1893,102 +1893,94 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A-7.1</t>
+          <t>A-6.7</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>电流与电压</t>
+          <t>流体压强与流速</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>电路 · 单元七：电流、电压与欧姆定律</t>
+          <t>压力与压强 · 单元六：压强与浮力</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ</t>
+          <t>Ⅰ</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>电流表要串联还是并联在电路中？</t>
+          <t>飞机为什么能飞起来？</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>07-电路-单元七-电流电压与欧姆定律.md</t>
+          <t>06-压强与浮力-单元六-压力与压强.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>A-7.2</t>
+          <t>A-6.8</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欧姆定律 电阻</t>
+          <t>液体对压强的传递</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>电路 · 单元七：电流、电压与欧姆定律</t>
+          <t>压力与压强 · 单元六：压强与浮力</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ</t>
+          <t>Ⅰ</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>电阻是导体本身的性质，还是随电压变化？</t>
+          <t>液压千斤顶为什么用小力就能顶起汽车？</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>07-电路-单元七-电流电压与欧姆定律.md</t>
+          <t>06-压强与浮力-单元六-压力与压强.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>A-7.3</t>
+          <t>A-7.1</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>串联电路</t>
+          <t>电流与电压</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2016,7 +2008,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>串联电路中，电流处处相等吗？</t>
+          <t>电流表要串联还是并联在电路中？</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2028,12 +2020,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A-7.4</t>
+          <t>A-7.2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>并联电路</t>
+          <t>欧姆定律 电阻</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2061,7 +2053,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>并联电路中，各支路电压相等吗？</t>
+          <t>电阻是导体本身的性质，还是随电压变化？</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2073,17 +2065,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>A-8.1</t>
+          <t>A-7.3</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>电功率</t>
+          <t>串联电路</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>电能与磁 · 单元八：电与磁</t>
+          <t>电路 · 单元七：电流、电压与欧姆定律</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2106,29 +2098,29 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>100 W 的灯泡一定比 40 W 的亮吗？</t>
+          <t>串联电路中，电流处处相等吗？</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>08-电能与磁-单元八-电与磁.md</t>
+          <t>07-电路-单元七-电流电压与欧姆定律.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>A-8.2</t>
+          <t>A-7.4</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>电流的磁场</t>
+          <t>并联电路</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>电能与磁 · 单元八：电与磁</t>
+          <t>电路 · 单元七：电流、电压与欧姆定律</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2151,24 +2143,24 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>通电导线周围有磁场吗？</t>
+          <t>并联电路中，各支路电压相等吗？</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>08-电能与磁-单元八-电与磁.md</t>
+          <t>07-电路-单元七-电流电压与欧姆定律.md</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>A-8.3</t>
+          <t>A-8.1</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>电能的获得和输送</t>
+          <t>电功率</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2178,21 +2170,25 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ</t>
+          <t>Ⅱ</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>发电机是把什么能转化成电能？</t>
+          <t>100 W 的灯泡一定比 40 W 的亮吗？</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2204,12 +2200,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>A-8.4</t>
+          <t>A-8.2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>无线电波与通信</t>
+          <t>电流的磁场</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2219,21 +2215,25 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ</t>
+          <t>Ⅱ</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>无线电波和光是不是同一种东西？</t>
+          <t>通电导线周围有磁场吗？</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2245,17 +2245,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A-9.1</t>
+          <t>A-8.3</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>原子</t>
+          <t>电能的获得和输送</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>从原子到星系 · 单元九：微观与宇宙</t>
+          <t>电能与磁 · 单元八：电与磁</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2274,29 +2274,29 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>原子还能再分吗？</t>
+          <t>发电机是把什么能转化成电能？</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>09-微观与宇宙-单元九-从原子到星系.md</t>
+          <t>08-电能与磁-单元八-电与磁.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>A-9.2</t>
+          <t>A-8.4</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>地球 太阳系</t>
+          <t>无线电波与通信</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>从原子到星系 · 单元九：微观与宇宙</t>
+          <t>电能与磁 · 单元八：电与磁</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2315,24 +2315,24 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>太阳系有几大行星？</t>
+          <t>无线电波和光是不是同一种东西？</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>09-微观与宇宙-单元九-从原子到星系.md</t>
+          <t>08-电能与磁-单元八-电与磁.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>A-9.3</t>
+          <t>A-9.1</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>银河系 宇宙</t>
+          <t>原子</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>宇宙在膨胀还是收缩？</t>
+          <t>原子还能再分吗？</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>A-9.4</t>
+          <t>A-9.2</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>能量的转化和守恒</t>
+          <t>地球 太阳系</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2383,35 +2383,117 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ</t>
+          <t>Ⅰ</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
+          <t>太阳系有几大行星？</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>09-微观与宇宙-单元九-从原子到星系.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>银河系 宇宙</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>从原子到星系 · 单元九：微观与宇宙</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>宇宙在膨胀还是收缩？</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>09-微观与宇宙-单元九-从原子到星系.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A-9.4</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>能量的转化和守恒</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>从原子到星系 · 单元九：微观与宇宙</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
           <t>能量会不会凭空消失？</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>09-微观与宇宙-单元九-从原子到星系.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I44"/>
+  <autoFilter ref="A1:I46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2422,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2462,7 +2544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A-1.1</t>
+          <t>A-0.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2482,14 +2564,14 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>对着山崖喊一声，2 s 后听到回声。声速取 340 m/s，求人到山崖的距离。</t>
+          <t>刻度尺分度值 1 mm，测得物体长度 2.35 cm。哪几位是准确的，哪一位是估读的？</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>A-1.1</t>
+          <t>A-0.1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2509,14 +2591,14 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>甲在铁管一端敲一下，乙在另一端听到两次声音，间隔 2.74 s。管长 1000 m，空气中声速 340 m/s。求声音在铁中的速度。</t>
+          <t>为什么多次测量取平均值能减小误差？</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A-1.1</t>
+          <t>A-0.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2536,14 +2618,14 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>声呐向海底发出超声波，4 s 后收到回波。海水声速 1500 m/s。 (1) 求海底深度； (2) 为什么用超声波而不用普通声音？ (3) 月球上能用声呐测距吗？</t>
+          <t>(1) 误差与错误的区别？ (2) 1.5 m 等于多少 nm？ (3) 为什么测量时要选合适量程的仪器？</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>A-1.2</t>
+          <t>A-1.1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2563,14 +2645,14 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>用同样大的力敲击装有不同高度水的瓶子（敲瓶身），水越多，音调越高还是越低？</t>
+          <t>对着山崖喊一声，2 s 后听到回声。声速取 340 m/s，求人到山崖的距离。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A-1.2</t>
+          <t>A-1.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2590,14 +2672,14 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>"震耳欲聋"和"尖声细语"分别描述声音的什么特征？</t>
+          <t>甲在铁管一端敲一下，乙在另一端听到两次声音，间隔 2.74 s。管长 1000 m，空气中声速 340 m/s。求声音在铁中的速度。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>A-1.2</t>
+          <t>A-1.1</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2617,14 +2699,14 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>用同样的力拨动吉他弦： (1) 弦越短，音调如何变化？ (2) 弦越细，音调如何变化？ (3) 弦绷得越紧，音调如何变化？</t>
+          <t>声呐向海底发出超声波，4 s 后收到回波。海水声速 1500 m/s。 (1) 求海底深度； (2) 为什么用超声波而不用普通声音？ (3) 月球上能用声呐测距吗？</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>A-1.2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2644,14 +2726,14 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>入射光线与镜面成 30°角，求入射角和反射角。</t>
+          <t>用同样大的力敲击装有不同高度水的瓶子（敲瓶身），水越多，音调越高还是越低？</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>A-1.2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2671,14 +2753,14 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>镜面反射与漫反射有什么区别？为什么我们能看到不发光的物体？</t>
+          <t>"震耳欲聋"和"尖声细语"分别描述声音的什么特征？</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>A-1.2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2698,14 +2780,14 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>一束光与镜面成 20°入射，保持入射光线不动，把镜面绕入射点转过 10°。 (1) 反射光线转过多少度？ (2) 为什么？</t>
+          <t>用同样的力拨动吉他弦： (1) 弦越短，音调如何变化？ (2) 弦越细，音调如何变化？ (3) 弦绷得越紧，音调如何变化？</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>A-2.2</t>
+          <t>A-2.1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2725,14 +2807,14 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>人站在镜前 2 m 处。像到镜面的距离是多少？人与像的距离是多少？</t>
+          <t>入射光线与镜面成 30°角，求入射角和反射角。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>A-2.2</t>
+          <t>A-2.1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2752,14 +2834,14 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>为什么照镜子时，人举起右手，像举的是左手？</t>
+          <t>镜面反射与漫反射有什么区别？为什么我们能看到不发光的物体？</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>A-2.2</t>
+          <t>A-2.1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2779,14 +2861,14 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>(1) 平面镜成像为什么是虚像？ (2) 实像和虚像有什么区别？ (3) 怎样用实验验证像与物等大？</t>
+          <t>一束光与镜面成 20°入射，保持入射光线不动，把镜面绕入射点转过 10°。 (1) 反射光线转过多少度？ (2) 为什么？</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>A-2.3</t>
+          <t>A-2.2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2806,14 +2888,14 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>光从空气斜射入水中，入射角 45°。折射角大于还是小于 45°？</t>
+          <t>人站在镜前 2 m 处。像到镜面的距离是多少？人与像的距离是多少？</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>A-2.3</t>
+          <t>A-2.2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2833,14 +2915,14 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>池水看起来比实际浅，为什么？</t>
+          <t>为什么照镜子时，人举起右手，像举的是左手？</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>A-2.3</t>
+          <t>A-2.2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2860,14 +2942,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>(1) 折射与反射有什么相同点和不同点？ (2) 为什么从水中看岸上的物体位置偏高？ (3) 海市蜃楼与折射有关吗？</t>
+          <t>(1) 平面镜成像为什么是虚像？ (2) 实像和虚像有什么区别？ (3) 怎样用实验验证像与物等大？</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A-2.4</t>
+          <t>A-2.3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2887,14 +2969,14 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>凸透镜焦距 10 cm，物体放在 30 cm 处。成什么样的像？</t>
+          <t>光从空气斜射入水中，入射角 45°。折射角大于还是小于 45°？</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>A-2.4</t>
+          <t>A-2.3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2914,14 +2996,14 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>用照相机拍全身像，想拍半身像，应该靠近还是远离？镜头怎么调？</t>
+          <t>池水看起来比实际浅，为什么？</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A-2.4</t>
+          <t>A-2.3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2941,14 +3023,14 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>(1) 为什么放大镜要靠近物体？ (2) 实像和虚像怎么区分？ (3) 近视眼镜是什么透镜？</t>
+          <t>(1) 折射与反射有什么相同点和不同点？ (2) 为什么从水中看岸上的物体位置偏高？ (3) 海市蜃楼与折射有关吗？</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A-2.5</t>
+          <t>A-2.4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2968,14 +3050,14 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>白光照在红纸上，纸呈什么颜色？为什么？</t>
+          <t>凸透镜焦距 10 cm，物体放在 30 cm 处。成什么样的像？</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A-2.5</t>
+          <t>A-2.4</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2995,14 +3077,14 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>为什么夏天穿白衣服比穿黑衣服凉快？</t>
+          <t>用照相机拍全身像，想拍半身像，应该靠近还是远离？镜头怎么调？</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A-2.5</t>
+          <t>A-2.4</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3022,14 +3104,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>(1) 彩虹是怎么形成的？ (2) 为什么雾天用黄光做车灯？ (3) 电视屏幕的三种荧光粉为什么是红绿蓝？</t>
+          <t>(1) 为什么放大镜要靠近物体？ (2) 实像和虚像怎么区分？ (3) 近视眼镜是什么透镜？</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>A-3.1</t>
+          <t>A-2.5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -3049,14 +3131,14 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>坐在行驶汽车里的人，以车为参照物是______，以路边的树为参照物是______。</t>
+          <t>白光照在红纸上，纸呈什么颜色？为什么？</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>A-3.1</t>
+          <t>A-2.5</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3076,14 +3158,14 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>"小小竹排江中游，巍巍青山两岸走"，分别以什么为参照物？</t>
+          <t>为什么夏天穿白衣服比穿黑衣服凉快？</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>A-3.1</t>
+          <t>A-2.5</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -3103,14 +3185,14 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>两列火车并排停靠，甲车启动时，甲车乘客觉得乙车在后退。 (1) 以什么为参照物？ (2) 实际乙车动了吗？ (3) 这说明了什么？</t>
+          <t>(1) 彩虹是怎么形成的？ (2) 为什么雾天用黄光做车灯？ (3) 电视屏幕的三种荧光粉为什么是红绿蓝？</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A-3.2</t>
+          <t>A-3.1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3130,14 +3212,14 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>100 m 跑 12.5 s，求速度（m/s 和 km/h）。</t>
+          <t>坐在行驶汽车里的人，以车为参照物是______，以路边的树为参照物是______。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>A-3.2</t>
+          <t>A-3.1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3157,14 +3239,14 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>汽车前一半路程 10 m/s，后一半路程 20 m/s。求全程平均速度。</t>
+          <t>"小小竹排江中游，巍巍青山两岸走"，分别以什么为参照物？</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>A-3.2</t>
+          <t>A-3.1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3184,14 +3266,14 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>甲车 20 m/s 行驶，乙车在甲前方 100 m 处以 10 m/s 同向行驶。 (1) 甲追上乙要多久？ (2) 追上时甲走了多远？</t>
+          <t>两列火车并排停靠，甲车启动时，甲车乘客觉得乙车在后退。 (1) 以什么为参照物？ (2) 实际乙车动了吗？ (3) 这说明了什么？</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A-3.3</t>
+          <t>A-3.2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3211,14 +3293,14 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>下列现象中，力改变了物体形状的是： A. 踢球 B. 压弹簧 C. 刹车 D. 抛石头</t>
+          <t>100 m 跑 12.5 s，求速度（m/s 和 km/h）。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A-3.3</t>
+          <t>A-3.2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3238,14 +3320,14 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>为什么游泳时手向后划水，人却向前进？</t>
+          <t>汽车前一半路程 10 m/s，后一半路程 20 m/s。求全程平均速度。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A-3.3</t>
+          <t>A-3.2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3265,14 +3347,14 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>用 5 N 的力沿水平方向向右推箱子，作用点在箱子左侧中部。 (1) 画出力的示意图要点； (2) 若力增大到 8 N，作用效果如何变？ (3) 若改为斜向上推，效果有何不同？</t>
+          <t>甲车 20 m/s 行驶，乙车在甲前方 100 m 处以 10 m/s 同向行驶。 (1) 甲追上乙要多久？ (2) 追上时甲走了多远？</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A-3.4</t>
+          <t>A-3.3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3292,14 +3374,14 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>质量 50 kg 的人，重力是多少？（g 取 10 N/kg）</t>
+          <t>下列现象中，力改变了物体形状的是： A. 踢球 B. 压弹簧 C. 刹车 D. 抛石头</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A-3.4</t>
+          <t>A-3.3</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3319,14 +3401,14 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>为什么建筑工人用重垂线检查墙壁是否竖直？</t>
+          <t>为什么游泳时手向后划水，人却向前进？</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>A-3.4</t>
+          <t>A-3.3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3346,14 +3428,14 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>物体在月球上重力约为地球的 1/6。 (1) 同一物体在月球上质量变吗？ (2) 重力变吗？ (3) 用弹簧测力计在月球上称同一物体，读数如何？</t>
+          <t>用 5 N 的力沿水平方向向右推箱子，作用点在箱子左侧中部。 (1) 画出力的示意图要点； (2) 若力增大到 8 N，作用效果如何变？ (3) 若改为斜向上推，效果有何不同？</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>A-3.5</t>
+          <t>A-3.4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3373,14 +3455,14 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>3 N 和 4 N 的两个力，同向和反向时的合力各是多少？</t>
+          <t>质量 50 kg 的人，重力是多少？（g 取 10 N/kg）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A-3.5</t>
+          <t>A-3.4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3400,14 +3482,14 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>物体受水平向右 10 N 和水平向左 4 N 的力，合力多大？方向如何？</t>
+          <t>为什么建筑工人用重垂线检查墙壁是否竖直？</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>A-3.5</t>
+          <t>A-3.4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3427,14 +3509,14 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>(1) 为什么说"合力不一定大于分力"？ (2) 两个力夹角 90° 时能直接加减吗？ (3) 三力平衡时合力是多少？</t>
+          <t>物体在月球上重力约为地球的 1/6。 (1) 同一物体在月球上质量变吗？ (2) 重力变吗？ (3) 用弹簧测力计在月球上称同一物体，读数如何？</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>A-3.6</t>
+          <t>A-3.5</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3454,14 +3536,14 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>静止在水平桌面上的书重 5 N。桌面对书的支持力多大？方向如何？</t>
+          <t>3 N 和 4 N 的两个力，同向和反向时的合力各是多少？</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>A-3.6</t>
+          <t>A-3.5</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3481,14 +3563,14 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>"书对桌面的压力"与"桌面对书的支持力"是平衡力吗？</t>
+          <t>物体受水平向右 10 N 和水平向左 4 N 的力，合力多大？方向如何？</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>A-3.6</t>
+          <t>A-3.5</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3508,14 +3590,14 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>(1) 匀速下降的跳伞运动员受哪两个力？什么关系？ (2) 加速下降时还平衡吗？ (3) 二力平衡与作用力反作用力的区别？</t>
+          <t>(1) 为什么说"合力不一定大于分力"？ (2) 两个力夹角 90° 时能直接加减吗？ (3) 三力平衡时合力是多少？</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A-3.7</t>
+          <t>A-3.6</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3535,14 +3617,14 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>汽车急刹车，乘客为什么向前倾？</t>
+          <t>静止在水平桌面上的书重 5 N。桌面对书的支持力多大？方向如何？</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>A-3.7</t>
+          <t>A-3.6</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3562,14 +3644,14 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>为什么说"牛顿第一定律不能用实验直接验证"？</t>
+          <t>"书对桌面的压力"与"桌面对书的支持力"是平衡力吗？</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>A-3.7</t>
+          <t>A-3.6</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3589,14 +3671,14 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>(1) 惯性大小由什么决定？ (2) 为什么货车要限载？ (3) 安全带的作用是什么？</t>
+          <t>(1) 匀速下降的跳伞运动员受哪两个力？什么关系？ (2) 加速下降时还平衡吗？ (3) 二力平衡与作用力反作用力的区别？</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>A-4.1</t>
+          <t>A-3.7</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3616,14 +3698,14 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>撬棒支点距石头 0.2 m，石头重 200 N，手在距支点 1 m 处。求最小的力。</t>
+          <t>汽车急刹车，乘客为什么向前倾？</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>A-4.1</t>
+          <t>A-3.7</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3643,14 +3725,14 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>下列工具中，属于省力杠杆的是：筷子、开瓶器、镊子、天平、钓鱼竿。</t>
+          <t>为什么说"牛顿第一定律不能用实验直接验证"？</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>A-4.1</t>
+          <t>A-3.7</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3670,14 +3752,14 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>一根 1 m 长的杠杆，左端挂 20 N，右端挂 30 N。 (1) 支点应放在哪里？ (2) 若支点移到中点，哪端下沉？ (3) 如何恢复平衡？</t>
+          <t>(1) 惯性大小由什么决定？ (2) 为什么货车要限载？ (3) 安全带的作用是什么？</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>A-4.2</t>
+          <t>A-4.1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3697,14 +3779,14 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>用动滑轮提升 100 N 的物体，至少需要多大的力？（不计摩擦和滑轮重）</t>
+          <t>撬棒支点距石头 0.2 m，石头重 200 N，手在距支点 1 m 处。求最小的力。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>A-4.2</t>
+          <t>A-4.1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3724,14 +3806,14 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>滑轮组由 2 个定滑轮和 2 个动滑轮组成，n = 4，提升 400 N 的物体。求拉力和绳子自由端移动的距离（物体升高 1 m）。</t>
+          <t>下列工具中，属于省力杠杆的是：筷子、开瓶器、镊子、天平、钓鱼竿。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>A-4.2</t>
+          <t>A-4.1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3751,14 +3833,14 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>(1) 定滑轮和动滑轮各有什么优缺点？ (2) 为什么滑轮组"省力必费距离"？ (3) 斜面和滑轮都能省力，原理相同吗？</t>
+          <t>一根 1 m 长的杠杆，左端挂 20 N，右端挂 30 N。 (1) 支点应放在哪里？ (2) 若支点移到中点，哪端下沉？ (3) 如何恢复平衡？</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>A-4.3</t>
+          <t>A-4.2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3778,14 +3860,14 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>用 50 N 的水平推力把箱子推了 4 m，用时 5 s。求功和功率。</t>
+          <t>用动滑轮提升 100 N 的物体，至少需要多大的力？（不计摩擦和滑轮重）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>A-4.3</t>
+          <t>A-4.2</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3805,14 +3887,14 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>提着 20 N 的水桶在水平路面上走 10 m，人对水桶做功多少？</t>
+          <t>滑轮组由 2 个定滑轮和 2 个动滑轮组成，n = 4，提升 400 N 的物体。求拉力和绳子自由端移动的距离（物体升高 1 m）。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>A-4.3</t>
+          <t>A-4.2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3832,14 +3914,14 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>(1) 三种不做功的情况？ (2) 为什么起重机标"功率"而不是"功"？ (3) 功率大的机械一定做功多吗？</t>
+          <t>(1) 定滑轮和动滑轮各有什么优缺点？ (2) 为什么滑轮组"省力必费距离"？ (3) 斜面和滑轮都能省力，原理相同吗？</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>A-4.4</t>
+          <t>A-4.3</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3859,14 +3941,14 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>同一小球从 2 m 和 4 m 高处自由下落，落地时动能哪个大？</t>
+          <t>用 50 N 的水平推力把箱子推了 4 m，用时 5 s。求功和功率。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>A-4.4</t>
+          <t>A-4.3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3886,14 +3968,14 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>滚摆从高处放下，描述能量转化过程。</t>
+          <t>提着 20 N 的水桶在水平路面上走 10 m，人对水桶做功多少？</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>A-4.4</t>
+          <t>A-4.3</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3913,14 +3995,14 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>(1) 跳伞运动员匀速下降时机械能如何变化？ (2) 为什么？ (3) 说明什么条件下机械能守恒？</t>
+          <t>(1) 三种不做功的情况？ (2) 为什么起重机标"功率"而不是"功"？ (3) 功率大的机械一定做功多吗？</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>A-4.5</t>
+          <t>A-4.4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3940,14 +4022,14 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>用滑轮组把 400 N 的物体提高 2 m，实际拉力 250 N，绳端移动 4 m。求有用功、总功、机械效率。</t>
+          <t>同一小球从 2 m 和 4 m 高处自由下落，落地时动能哪个大？</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>A-4.5</t>
+          <t>A-4.4</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3967,14 +4049,14 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>为什么机械效率总小于 100%？</t>
+          <t>滚摆从高处放下，描述能量转化过程。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>A-4.5</t>
+          <t>A-4.4</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3994,14 +4076,14 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>(1) 省力机械为什么费距离？ (2) 有没有既省力又省距离的机械？ (3) 机械效率与功率有什么区别？</t>
+          <t>(1) 跳伞运动员匀速下降时机械能如何变化？ (2) 为什么？ (3) 说明什么条件下机械能守恒？</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>A-5.1</t>
+          <t>A-4.5</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -4021,14 +4103,14 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>温度计的正确使用方法是？</t>
+          <t>用滑轮组把 400 N 的物体提高 2 m，实际拉力 250 N，绳端移动 4 m。求有用功、总功、机械效率。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>A-5.1</t>
+          <t>A-4.5</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4048,14 +4130,14 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>"今天很热"和"这杯水很热"，这里的"热"含义相同吗？</t>
+          <t>为什么机械效率总小于 100%？</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>A-5.1</t>
+          <t>A-4.5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -4075,14 +4157,14 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>(1) 体温计为什么能离开人体读数？ (2) 它和普通温度计有什么结构差异？ (3) 使用前要做什么？</t>
+          <t>(1) 省力机械为什么费距离？ (2) 有没有既省力又省距离的机械？ (3) 机械效率与功率有什么区别？</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>A-5.2</t>
+          <t>A-5.1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4102,14 +4184,14 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>2 kg 水从 20 ℃ 加热到 80 ℃，吸收多少热量？</t>
+          <t>温度计的正确使用方法是？</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>A-5.2</t>
+          <t>A-5.1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -4129,14 +4211,14 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>为什么沿海地区昼夜温差比内陆小？</t>
+          <t>"今天很热"和"这杯水很热"，这里的"热"含义相同吗？</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>A-5.2</t>
+          <t>A-5.1</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4156,14 +4238,14 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>把 200 g、80 ℃ 的热水倒入 300 g、20 ℃ 的冷水中，不计热损失。求混合后的温度。</t>
+          <t>(1) 体温计为什么能离开人体读数？ (2) 它和普通温度计有什么结构差异？ (3) 使用前要做什么？</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>A-5.3</t>
+          <t>A-5.2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4183,14 +4265,14 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>0 ℃ 的冰有内能吗？为什么？</t>
+          <t>2 kg 水从 20 ℃ 加热到 80 ℃，吸收多少热量？</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>A-5.3</t>
+          <t>A-5.2</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4210,14 +4292,14 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>"摩擦生热"和"晒太阳变暖"分别是通过什么方式改变内能？</t>
+          <t>为什么沿海地区昼夜温差比内陆小？</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>A-5.3</t>
+          <t>A-5.2</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -4237,14 +4319,14 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>(1) 冰熔化时温度不变，内能变吗？ (2) 为什么？ (3) 内能与机械能有什么区别？</t>
+          <t>把 200 g、80 ℃ 的热水倒入 300 g、20 ℃ 的冷水中，不计热损失。求混合后的温度。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>A-5.4</t>
+          <t>A-5.3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4264,14 +4346,14 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>冰棒从冰箱取出后冒"白气"，是什么现象？</t>
+          <t>0 ℃ 的冰有内能吗？为什么？</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>A-5.4</t>
+          <t>A-5.3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4291,14 +4373,14 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>为什么夏天在教室里洒水会凉快？</t>
+          <t>"摩擦生热"和"晒太阳变暖"分别是通过什么方式改变内能？</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>A-5.4</t>
+          <t>A-5.3</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4318,14 +4400,14 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>(1) 晶体熔化的特点？ (2) 为什么"下雪不冷化雪冷"？ (3) 干冰升华有什么用途？</t>
+          <t>(1) 冰熔化时温度不变，内能变吗？ (2) 为什么？ (3) 内能与机械能有什么区别？</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>A-5.5</t>
+          <t>A-5.4</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -4345,14 +4427,14 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>汽油机一个工作循环中，活塞往复几次？对外做功几次？</t>
+          <t>冰棒从冰箱取出后冒"白气"，是什么现象？</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>A-5.5</t>
+          <t>A-5.4</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4372,14 +4454,14 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>完全燃烧 0.5 kg 汽油（热值 4.6×10⁷ J/kg），放出多少热量？若热机效率 30%，做多少有用功？</t>
+          <t>为什么夏天在教室里洒水会凉快？</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>A-5.5</t>
+          <t>A-5.4</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -4399,14 +4481,14 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>(1) 为什么热机效率总小于 100%？ (2) 提高效率的途径？ (3) 热机对环境的影响？</t>
+          <t>(1) 晶体熔化的特点？ (2) 为什么"下雪不冷化雪冷"？ (3) 干冰升华有什么用途？</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>A-6.1</t>
+          <t>A-5.5</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4426,14 +4508,14 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>某金属块质量 540 g，体积 200 cm³。求密度，并判断是什么金属。</t>
+          <t>汽油机一个工作循环中，活塞往复几次？对外做功几次？</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>A-6.1</t>
+          <t>A-5.5</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4453,14 +4535,14 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>一瓶水倒掉一半，密度、质量、体积各如何变化？</t>
+          <t>完全燃烧 0.5 kg 汽油（热值 4.6×10⁷ J/kg），放出多少热量？若热机效率 30%，做多少有用功？</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>A-6.1</t>
+          <t>A-5.5</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4480,14 +4562,14 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>一个瓶子最多装 500 g 水。 (1) 瓶的容积是多少？ (2) 若改装酒精（0.8 g/cm³），能装多少克？ (3) 为什么用密度判断物质种类要测体积？</t>
+          <t>(1) 为什么热机效率总小于 100%？ (2) 提高效率的途径？ (3) 热机对环境的影响？</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>A-6.2</t>
+          <t>A-6.1</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4507,14 +4589,14 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>重 200 N 的物体放在 0.5 m² 的水平面上。求压强。</t>
+          <t>某金属块质量 540 g，体积 200 cm³。求密度，并判断是什么金属。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>A-6.2</t>
+          <t>A-6.1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4534,14 +4616,14 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>为什么书包带要做得很宽？</t>
+          <t>一瓶水倒掉一半，密度、质量、体积各如何变化？</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>A-6.2</t>
+          <t>A-6.1</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4561,14 +4643,14 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>(1) 增大压强的两种方法，各举一例。 (2) 减小压强的两种方法，各举一例。 (3) 为什么坦克要装履带？</t>
+          <t>一个瓶子最多装 500 g 水。 (1) 瓶的容积是多少？ (2) 若改装酒精（0.8 g/cm³），能装多少克？ (3) 为什么用密度判断物质种类要测体积？</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>A-6.3</t>
+          <t>A-6.2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4588,14 +4670,14 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>水深 0.5 m 处，水的压强是多少？（g 取 10）</t>
+          <t>重 200 N 的物体放在 0.5 m² 的水平面上。求压强。</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>A-6.3</t>
+          <t>A-6.2</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4615,14 +4697,14 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>为什么水坝要做成"上窄下宽"？</t>
+          <t>为什么书包带要做得很宽？</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>A-6.3</t>
+          <t>A-6.2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4642,14 +4724,14 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>两个容器底面积相同，装入同样深度的水，形状不同（一个直筒、一个上大下小）。 (1) 底部压强相同吗？ (2) 底部压力相同吗？ (3) 为什么？</t>
+          <t>(1) 增大压强的两种方法，各举一例。 (2) 减小压强的两种方法，各举一例。 (3) 为什么坦克要装履带？</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>A-6.4</t>
+          <t>A-6.3</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -4669,14 +4751,14 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>物体排开 100 cm³ 的水，浮力多大？（g 取 10）</t>
+          <t>水深 0.5 m 处，水的压强是多少？（g 取 10）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>A-6.4</t>
+          <t>A-6.3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4696,14 +4778,14 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>同一物体浸没在水和酒精中，哪次浮力大？</t>
+          <t>为什么水坝要做成"上窄下宽"？</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>A-6.4</t>
+          <t>A-6.3</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4723,14 +4805,14 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>(1) 为什么木头浮在水面，铁块沉底？ (2) 浮力与深度无关，为什么越往深处越"压"？ (3) 如何用弹簧测力计测浮力？</t>
+          <t>两个容器底面积相同，装入同样深度的水，形状不同（一个直筒、一个上大下小）。 (1) 底部压强相同吗？ (2) 底部压力相同吗？ (3) 为什么？</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>A-6.5</t>
+          <t>A-6.4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4750,14 +4832,14 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>木块漂浮在水面上，重力 5 N。浮力多大？</t>
+          <t>物体排开 100 cm³ 的水，浮力多大？（g 取 10）</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>A-6.5</t>
+          <t>A-6.4</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4777,14 +4859,14 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>同一鸡蛋在清水下沉、在浓盐水中漂浮。说明什么？</t>
+          <t>同一物体浸没在水和酒精中，哪次浮力大？</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>A-6.5</t>
+          <t>A-6.4</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4804,14 +4886,14 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>(1) 悬浮与漂浮的区别？ (2) 潜水艇如何实现上浮下潜？ (3) 为什么冰块漂浮时露出约 1/10？</t>
+          <t>(1) 为什么木头浮在水面，铁块沉底？ (2) 浮力与深度无关，为什么越往深处越"压"？ (3) 如何用弹簧测力计测浮力？</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>A-6.6</t>
+          <t>A-6.5</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -4831,14 +4913,14 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>为什么用吸管能吸上饮料？</t>
+          <t>木块漂浮在水面上，重力 5 N。浮力多大？</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>A-6.6</t>
+          <t>A-6.5</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4858,14 +4940,14 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>为什么在高山上煮饭不容易熟？</t>
+          <t>同一鸡蛋在清水下沉、在浓盐水中漂浮。说明什么？</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>A-6.6</t>
+          <t>A-6.5</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -4885,14 +4967,14 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>(1) 托里拆利实验为什么用水银？ (2) 若用水做，需要多长的管？ (3) 哪些因素会影响测量结果？</t>
+          <t>(1) 悬浮与漂浮的区别？ (2) 潜水艇如何实现上浮下潜？ (3) 为什么冰块漂浮时露出约 1/10？</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>A-6.7</t>
+          <t>A-6.6</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4912,14 +4994,14 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>为什么火车站要设安全线？</t>
+          <t>为什么用吸管能吸上饮料？</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>A-6.7</t>
+          <t>A-6.6</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -4939,14 +5021,14 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>飞机机翼为什么上凸下平？</t>
+          <t>为什么在高山上煮饭不容易熟？</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>A-6.7</t>
+          <t>A-6.6</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4966,14 +5048,14 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>(1) 喷雾器的工作原理？ (2) 为什么乒乓球能在漏斗里"悬浮"？ (3) 风大时为什么伞容易被"吸"翻？</t>
+          <t>(1) 托里拆利实验为什么用水银？ (2) 若用水做，需要多长的管？ (3) 哪些因素会影响测量结果？</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>A-7.1</t>
+          <t>A-6.7</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -4993,14 +5075,14 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>家庭电路的电压是多少？一节干电池呢？</t>
+          <t>为什么火车站要设安全线？</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>A-7.1</t>
+          <t>A-6.7</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5020,14 +5102,14 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>电流表并联在灯泡两端会发生什么？</t>
+          <t>飞机机翼为什么上凸下平？</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>A-7.1</t>
+          <t>A-6.7</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5047,14 +5129,14 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>(1) 电流是怎样形成的？ (2) 电压的作用是什么？ (3) 为什么说"电压是形成电流的原因"？</t>
+          <t>(1) 喷雾器的工作原理？ (2) 为什么乒乓球能在漏斗里"悬浮"？ (3) 风大时为什么伞容易被"吸"翻？</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>A-7.2</t>
+          <t>A-6.8</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5074,14 +5156,14 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>导体两端电压 6 V，通过电流 0.3 A。求电阻。</t>
+          <t>液压机小活塞面积 10 cm²，大活塞 100 cm²，小活塞受力 200 N。大活塞能举起多重的物体？</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>A-7.2</t>
+          <t>A-6.8</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -5101,14 +5183,14 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>"导体的电阻与电压成正比、与电流成反比"这句话对吗？</t>
+          <t>为什么液压机省力但不省功？</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>A-7.2</t>
+          <t>A-6.8</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5128,14 +5210,14 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>(1) 为什么灯丝通常在开灯瞬间容易烧断？ (2) 电阻与温度有什么关系？ (3) 滑动变阻器靠改变什么来变阻？</t>
+          <t>(1) 帕斯卡定律的适用条件？ (2) 液压刹车利用了这条规律吗？ (3) 为什么液压传动比机械传动平稳？</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>A-7.3</t>
+          <t>A-7.1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -5155,14 +5237,14 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>R₁ = 2 Ω、R₂ = 4 Ω 串联接在 6 V 电源上。求电流和各电阻两端电压。</t>
+          <t>家庭电路的电压是多少？一节干电池呢？</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>A-7.3</t>
+          <t>A-7.1</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5182,14 +5264,14 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>为什么串联电路中，电阻大的分到的电压大？</t>
+          <t>电流表并联在灯泡两端会发生什么？</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>A-7.3</t>
+          <t>A-7.1</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -5209,14 +5291,14 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>(1) 串联电路有什么优点和缺点？ (2) 为什么节日彩灯常串联？ (3) 一个灯坏了，其他灯为什么不亮？</t>
+          <t>(1) 电流是怎样形成的？ (2) 电压的作用是什么？ (3) 为什么说"电压是形成电流的原因"？</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>A-7.4</t>
+          <t>A-7.2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5236,14 +5318,14 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>R₁ = 2 Ω、R₂ = 3 Ω 并联接在 6 V 电源上。求各支路电流、干路电流、总电阻。</t>
+          <t>导体两端电压 6 V，通过电流 0.3 A。求电阻。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>A-7.4</t>
+          <t>A-7.2</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -5263,14 +5345,14 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>为什么家庭电路中的用电器要并联？</t>
+          <t>"导体的电阻与电压成正比、与电流成反比"这句话对吗？</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>A-7.4</t>
+          <t>A-7.2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5290,14 +5372,14 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>(1) 并联电路中，电阻小的支路电流大还是小？ (2) 为什么？ (3) 并联总电阻为什么小于任一分电阻？</t>
+          <t>(1) 为什么灯丝通常在开灯瞬间容易烧断？ (2) 电阻与温度有什么关系？ (3) 滑动变阻器靠改变什么来变阻？</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>A-8.1</t>
+          <t>A-7.3</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -5317,14 +5399,14 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>"220 V 100 W"的灯泡正常发光时，电流多大？电阻多大？</t>
+          <t>R₁ = 2 Ω、R₂ = 4 Ω 串联接在 6 V 电源上。求电流和各电阻两端电压。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>A-8.1</t>
+          <t>A-7.3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5344,14 +5426,14 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>1 度电可供 1000 W 的电器工作多久？</t>
+          <t>为什么串联电路中，电阻大的分到的电压大？</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>A-8.1</t>
+          <t>A-7.3</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -5371,14 +5453,14 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>两只灯泡"220 V 100 W"和"220 V 40 W"串联接在 220 V 电路上。 (1) 谁更亮？ (2) 为什么？ (3) 并联时呢？</t>
+          <t>(1) 串联电路有什么优点和缺点？ (2) 为什么节日彩灯常串联？ (3) 一个灯坏了，其他灯为什么不亮？</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>A-8.2</t>
+          <t>A-7.4</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5398,14 +5480,14 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>通电螺线管中电流方向从上往下看为顺时针。N 极在哪端？</t>
+          <t>R₁ = 2 Ω、R₂ = 3 Ω 并联接在 6 V 电源上。求各支路电流、干路电流、总电阻。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>A-8.2</t>
+          <t>A-7.4</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -5425,14 +5507,14 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>电磁铁与永磁体相比有什么优点？</t>
+          <t>为什么家庭电路中的用电器要并联？</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>A-8.2</t>
+          <t>A-7.4</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5452,14 +5534,14 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>(1) 怎样使电磁铁磁性增强？ (2) 电铃的工作原理？ (3) 磁悬浮列车利用了什么？</t>
+          <t>(1) 并联电路中，电阻小的支路电流大还是小？ (2) 为什么？ (3) 并联总电阻为什么小于任一分电阻？</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>A-8.3</t>
+          <t>A-8.1</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -5479,14 +5561,14 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>发电机和电动机的能量转化方向分别是什么？</t>
+          <t>"220 V 100 W"的灯泡正常发光时，电流多大？电阻多大？</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>A-8.3</t>
+          <t>A-8.1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5506,14 +5588,14 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>为什么远距离输电要用高压？</t>
+          <t>1 度电可供 1000 W 的电器工作多久？</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>A-8.3</t>
+          <t>A-8.1</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -5533,14 +5615,14 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>(1) 发电机的基本构造？ (2) 为什么家用电器用交流电？ (3) 变压器的作用？</t>
+          <t>两只灯泡"220 V 100 W"和"220 V 40 W"串联接在 220 V 电路上。 (1) 谁更亮？ (2) 为什么？ (3) 并联时呢？</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>A-8.4</t>
+          <t>A-8.2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5560,14 +5642,14 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>某广播频率 100 MHz，波长多少？</t>
+          <t>通电螺线管中电流方向从上往下看为顺时针。N 极在哪端？</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>A-8.4</t>
+          <t>A-8.2</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -5587,14 +5669,14 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>为什么手机在电梯里没信号，但在真空中（卫星）能通信？</t>
+          <t>电磁铁与永磁体相比有什么优点？</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>A-8.4</t>
+          <t>A-8.2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5614,14 +5696,14 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>(1) 电磁波与声波的本质区别？ (2) 为什么用光纤通信？ (3) 5G 为什么比 4G 快？</t>
+          <t>(1) 怎样使电磁铁磁性增强？ (2) 电铃的工作原理？ (3) 磁悬浮列车利用了什么？</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>A-9.1</t>
+          <t>A-8.3</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -5641,14 +5723,14 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>原子由哪些部分组成？各部分带电情况如何？</t>
+          <t>发电机和电动机的能量转化方向分别是什么？</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>A-9.1</t>
+          <t>A-8.3</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5668,14 +5750,14 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>摩擦起电的实质是什么？</t>
+          <t>为什么远距离输电要用高压？</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>A-9.1</t>
+          <t>A-8.3</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -5695,14 +5777,14 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>(1) 分子、原子、原子核的大小关系？ (2) 为什么说"原子内部很空"？ (3) 原子核由什么维持？</t>
+          <t>(1) 发电机的基本构造？ (2) 为什么家用电器用交流电？ (3) 变压器的作用？</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>A-9.2</t>
+          <t>A-8.4</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5722,14 +5804,14 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>按离太阳由近到远，写出八大行星。</t>
+          <t>某广播频率 100 MHz，波长多少？</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>A-9.2</t>
+          <t>A-8.4</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -5749,14 +5831,14 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>"光年"是什么单位？1 光年约多少？</t>
+          <t>为什么手机在电梯里没信号，但在真空中（卫星）能通信？</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>A-9.2</t>
+          <t>A-8.4</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -5776,14 +5858,14 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>(1) 为什么行星绕太阳转？ (2) 四季是怎么形成的？ (3) 日食、月食的原理？</t>
+          <t>(1) 电磁波与声波的本质区别？ (2) 为什么用光纤通信？ (3) 5G 为什么比 4G 快？</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>A-9.3</t>
+          <t>A-9.1</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -5803,14 +5885,14 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>星系光谱红移说明什么？</t>
+          <t>原子由哪些部分组成？各部分带电情况如何？</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>A-9.3</t>
+          <t>A-9.1</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -5830,14 +5912,14 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>为什么说"宇宙膨胀没有中心"？</t>
+          <t>摩擦起电的实质是什么？</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>A-9.3</t>
+          <t>A-9.1</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -5857,14 +5939,14 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>(1) 大爆炸的证据有哪些？ (2) 宇宙的最终命运可能是什么？ (3) 人类为什么要探索宇宙？</t>
+          <t>(1) 分子、原子、原子核的大小关系？ (2) 为什么说"原子内部很空"？ (3) 原子核由什么维持？</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>A-9.4</t>
+          <t>A-9.2</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -5884,14 +5966,14 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>电灯发光时，能量如何转化？</t>
+          <t>按离太阳由近到远，写出八大行星。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>A-9.4</t>
+          <t>A-9.2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -5911,39 +5993,201 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>为什么"能量守恒"与"能源危机"不矛盾？</t>
+          <t>"光年"是什么单位？1 光年约多少？</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>(1) 为什么行星绕太阳转？ (2) 四季是怎么形成的？ (3) 日食、月食的原理？</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>星系光谱红移说明什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>为什么说"宇宙膨胀没有中心"？</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>(1) 大爆炸的证据有哪些？ (2) 宇宙的最终命运可能是什么？ (3) 人类为什么要探索宇宙？</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
           <t>A-9.4</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>电灯发光时，能量如何转化？</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>A-9.4</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>为什么"能量守恒"与"能源危机"不矛盾？</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>A-9.4</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>例3</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>(1) 举出三个能量转化的例子。 (2) 为什么永动机不可能制成？ (3) 能量转化效率为什么总小于 1？</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E130"/>
+  <autoFilter ref="A1:E136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8531,7 +8775,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9 个单元 / 43 个考点 / 129 道例题 / 59 条公式</t>
+          <t>10 个单元 / 45 个考点 / 135 道例题 / 59 条公式</t>
         </is>
       </c>
     </row>
